--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/feb-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/feb-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/feb-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/feb-2026.xlsx
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Antofagasta</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN D</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL LIBERTADOR GENERA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Santa Rosa</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Centro de Referencia de Salud Hospital Provincia Cordillera</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/feb-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/feb-2026.xlsx
@@ -562,7 +562,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1533,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1598,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1663,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1728,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1793,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1858,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1923,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1988,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2053,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2118,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2183,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2248,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2313,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2378,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2443,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2508,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2573,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2638,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2703,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2768,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2833,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2898,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2963,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3028,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3093,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3158,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3223,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3288,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3353,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3418,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3483,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3548,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3613,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3678,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3743,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3808,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3873,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3938,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4064,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4190,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4255,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4320,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4385,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4511,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4576,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4641,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4706,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4771,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4836,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4901,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4966,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5031,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5157,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5222,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5287,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5535,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5600,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5665,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5730,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5856,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5921,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5986,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6051,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6116,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6181,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6246,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6311,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6376,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6441,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6506,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6571,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6636,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6701,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6766,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6831,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6957,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7022,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7087,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7396,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7461,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7648,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7713,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7778,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7843,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7908,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7973,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8038,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8103,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8168,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8233,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8298,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8363,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8428,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8554,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8745,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8810,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8875,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8940,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +9005,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +9070,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +9257,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9322,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9448,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9513,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9106,7 +9578,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9643,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9708,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9834,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9899,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9964,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +10029,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +10094,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10159,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10224,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9777,7 +10289,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10354,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10419,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10484,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10021,7 +10549,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10736,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10801,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10866,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +10931,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10996,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +11061,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +11126,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +11191,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10753,7 +11317,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10814,7 +11382,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11447,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11512,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11577,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11642,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11707,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11833,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11302,7 +11898,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11963,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +12028,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +12093,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12158,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12223,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +12288,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12353,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
